--- a/2/免疫文献提取结果.xlsx
+++ b/2/免疫文献提取结果.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:L59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,40 +436,55 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>chapter</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>choose</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>explanation</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>file_path</t>
         </is>
@@ -481,243 +496,3405 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>第一章 绪言</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>大型光伏电站建设对共和盆地土壤细菌群落的影响</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>单选</t>
+          <t>张</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>药理学研究</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>药物对人体的作用,机体对药物的反应,药物的体内变化,药物作用的两面性,药物与机体的相互作用</t>
+          <t>中国沙漠</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>2024年7月</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>药理学是研究药物与机体（包括人体、病原体等）之间相互作用规律的科学。其研究内容主要包括两方面：药效学（药物对机体的作用）和药动学（机体对药物的处置过程）。选项A、B、C都只描述了其中一个方面，不全面。选项D“药物作用的两面性”只是药效学中的一个特点。因此，最完整、准确的表述是“药物与机体的相互作用”，因此正确选项是E。</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>药理学学习指导与习题集pdf.pdf</t>
+          <t>青海省共和县塔拉滩某大型光伏电站</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>100.6333</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>36.1500</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>大型光伏电站建设对共和盆地土壤细菌群落的影响_张晴.pdf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>第一章 绪言</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>Solar photovoltaic panels significantly promote vegetation recovery by modifying the soil surface microhabitats in an arid sandy ecosystem</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>单选</t>
+          <t>Liu</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>药物是指</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>能干扰细胞代谢的化学物质,能影响细胞功能的化学物质,能改变细胞形态的化学物质,用于治疗、预防和诊断疾病的化学物质,具有营养、保健、康复作用的化学物质</t>
+          <t>Land Degradation &amp; Development</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>2018年7月</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>药物是指用于治疗、预防和诊断疾病的化学物质。选项A、B、C描述过于宽泛，不能准确定义药物。选项E描述的是保健品或食品的功能，并非药物的核心定义。因此，正确选项是D。</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>药理学学习指导与习题集pdf.pdf</t>
+          <t>宁夏回族自治区银川市兴庆区宝丰太阳能光伏电站（位于毛乌素沙漠西南边缘）</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>106.6131</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>38.5325</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Solar photovoltaic panels significantly promote vegetation recovery by modifying the soil surface microhabitats in an arid sandy ecosystem.pdf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>第一章 绪言</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>The influence of wind farm development on the hydrochemistry and ecology of an upland stream</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>单选</t>
+          <t>Millidine</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>药动学主要研究</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>药物如何影响机体,机体如何处置药物,药物如何到达作用部位,机体如何清除药物,药物与机体的相互作用</t>
+          <t>Environmental Monitoring and Assessment</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>2003年至2007年</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>药动学（药代动力学）主要研究机体对药物的处置过程，包括药物在体内的吸收、分布、代谢（生物转化）和排泄的动态变化规律。选项A描述的是药效学的研究范畴。选项C和D是药动学研究的具体环节，但不全面。选项E是药理学的总研究范畴。因此，最准确的表述是“机体如何处置药物”，正确选项是B。</t>
+          <t>英国</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>药理学学习指导与习题集pdf.pdf</t>
+          <t>苏格兰斯佩河支流Allt a' Gheallaidh（处理流域）与Tulchan Burn（对照流域）</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>The influence of wind farm development on the hydrochemistry and ecology of an upland stream.pdf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>第一章 绪言</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>Aquatic Habitat Bird Occurrences at Photovoltaic Solar Energy Development in Southern California, USA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>英文</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>单选</t>
+          <t>Kosciuch</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>世界上第一部由政府颁布的药典是</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>《本草纲目》,《神农本草经》,《新修本草》,《英国药典》,《美国药典》</t>
+          <t>Diversity</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>2018年9月至11月及2019年9月至11月</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>我国唐代（公元659年）的《新修本草》是世界上第一部由政府颁布的药典。选项A《本草纲目》是明代李时珍的著作，影响深远但非第一部官修药典。选项B《神农本草经》是我国最早的药物学著作，但非政府颁布的药典。选项D和E是其他国家的药典，时间晚于《新修本草》。因此，正确选项是C。</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>药理学学习指导与习题集pdf.pdf</t>
+          <t>美国加利福尼亚州南部</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Aquatic Habitat Bird Occurrences at Photovoltaic Solar Energy Development in Southern California, USA.pdf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>第一章 绪言</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>Ecovoltaics: Maintaining Native Plants and Wash Connectivity inside a Mojave Desert Solar Facility Leads to Favorable Growing Conditions</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>单选</t>
+          <t>Wynne-Sison</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>关于新药的I期临床试验，以下叙述正确的是</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>首先观察的是药物的安全性，而不是药效,受试者只能是健康志愿者,可以采用随机双盲试验方法,为保证受试者安全，只进行单剂量给药后的研究,一般观察例数超过100例</t>
+          <t>Land</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>2018年至2020年</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>I期临床试验是初步的临床药理学及人体安全性评价试验，主要目的是观察人体对于新药的耐受程度和药代动力学，为制定给药方案提供依据。其核心是评估安全性，而非药效。选项B错误，I期受试者可以是健康志愿者或患者。选项C错误，I期通常为开放试验，不采用双盲。选项D错误，I期可能包括单次和多次给药研究。选项E错误，I期观察例数通常较少（20-30例）。因此，正确选项是A。</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>药理学学习指导与习题集pdf.pdf</t>
+          <t>内华达州帕朗普市山谷电力太阳能设施</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-115.972111</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>36.275278</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Ecovoltaics-Maintaining Native Plants and Wash Connectivity inside a Mojave Desert Solar Facility Leads to Favorable Growing Conditions.pdf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>第一章 绪言</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>Do wind turbines impact plant community properties in mountain region?</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>单选</t>
+          <t>Pătru-Stupariu</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>有临床疗效的药物</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>都能进入体内,都能改变机体的代谢或功能,都没有明显毒性,不一定有药理活性,不一定有主观或客观疗效指标的反应</t>
+          <t>Biologia</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>2015年5月</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>有临床疗效的药物不一定本身具有药理活性。例如，某些药物（前药）需在体内代谢后才产生活性；某些药物（如解毒药）通过物理化学作用（如络合）发挥疗效，而非通过药理作用。选项A、B、C、E的表述过于绝对。因此，正确选项是D。</t>
+          <t>罗马尼亚</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>药理学学习指导与习题集pdf.pdf</t>
+          <t>罗马尼亚喀尔巴阡山脉南部，梅赫丁齐山脉，托普莱茨地区，梅特里兹-德拉尼克峰附近</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>22.421944</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>44.773333</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Do wind turbines impact plant community properties.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Solar park microclimate and vegetation management effects on grassland carbon cycling</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>英文</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Armstrong</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Environmental Research Letters</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2013年6月27日至2014年6月27日</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>英国</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Westmill Solar Park</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-1.645833</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>51.6175</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Solar park microclimate and vegetation management effects on grassland carbon cycling.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Exploring a path of vegetation restoration best suited for a photovoltaic plant in the Hobq desert</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>英文</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Cai</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Frontiers in Environmental Science</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2022年6月</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>内蒙古自治区鄂尔多斯市杭锦旗独贵塔拉镇伊力光伏生态园</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>108.8356</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>40.4353</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Exploring a path of vegetation restoration best suited for a photovoltaic plant in the Hobq desert.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>光伏板高度对旱季石漠化地区不同坡度土壤性质的影响</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>水土保持通报</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2023年11月、2024年5月</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>云南省昆明市石林彝族自治县生态农业光伏试验示范基地</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>103.41027777777778</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>24.83388888888889</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>光伏板高度对旱季石漠化地区不同坡度土壤性质的影响_高文娇.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>不同植被恢复模式下光伏电站土壤有机碳储量分布特征</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>赵</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>浙江农林大学学报</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2019年6月</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>内蒙古自治区呼和浩特市土默特左旗沙尔沁乡的大有光能源光伏农林牧示范基地</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>110.7833</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>40.6000</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>不同植被恢复模式下光伏电站土壤有机碳储量分布特征_赵晶.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Impact of solar panels on runoff generation process</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Baiamonte</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Hydrological Processes</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>未明确说明</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>意大利</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>西西里岛阿格里真托省圣玛格丽塔贝利切</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>13.046983</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>37.695289</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Impact of solar panels on runoff generation process.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Effects of photovoltaic power station construction on terrestrial ecosystems: A meta-analysis</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Frontiers in Ecology and Evolution</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2023年3月</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>无特定研究区域（荟萃分析）</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>R-Effects of photovoltaic power station construction on terrestrial ecosystems-A meta-analysis.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>光伏发电站对高寒草甸土壤细菌群落组成及多样性的影响研究</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>孙</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>草地学报</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2022年7月</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>甘肃省甘南藏族自治州玛曲县尼玛镇拜尔多合光伏电站</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>102.151667</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>33.670278</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>光伏发电站对高寒草甸土壤细菌群落组成及多样性的影响研究_孙文倩.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Short- and long-term effects of an offshore wind farm on three species of sandeel and their sand habitat</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>van Deurs</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>MARINE ECOLOGY PROGRESS SERIES</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2002年3月至2010年3月</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>丹麦</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>北海，丹麦西海岸霍恩礁I号海上风电场附近</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>7.84</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>55.48</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Short- and long-term effects of an offshore wind farm on three species of sandeel and their sand habitat.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Effects of Revegetation on Soil Physical and Chemical Properties in Solar Photovoltaic Infrastructure</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Choi</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Frontiers in Environmental Science</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2017年7月</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>科罗拉多州杰斐逊县国家可再生能源实验室国家风能技术中心</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Effects of Revegetation on Soil Physical and Chemical Properties in Solar Photovoltaic Infrastructure.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Remarkable agrivoltaic influence on soil moisture, micrometeorology and water-use efficiency</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Hassanpour Adeh</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>PLOS ONE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2015年5月至8月</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>俄勒冈州立大学科瓦利斯校区Rabbit Hills农业光伏太阳能阵列</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-123.279</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>44.564</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Remarkable agrivoltaic influence on soil.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Solar park management and design to boost bumble bee populations</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Blaydes</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Environmental Research Letters</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2020年3月</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>英国</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>英格兰</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Solar park management and design to boost bumble bee populations.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Insectivorous bats alter their flight and feeding behaviour at ground-mounted solar farms</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Barré</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Journal of Applied Ecology</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2022年9月</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>法国</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>罗纳河谷</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Insectivorous bats alter their flight and feeding behaviour at ground-mounted solar farms.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Metagenomic biodiversity assessment within an offshore wind farm</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Serivichyaswat</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Scientific Reports</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2023年10月</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>丹麦</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>丹麦北海，日德兰半岛西海岸外的Horns Rev 1海上风电场</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Metagenomic biodiversity assessment within an offshore wind farm.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>光伏电站对沉陷塘冬季水质和浮游植物群落结构的影响</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Wang</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>水土保持通报</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2022年12月</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>安徽省淮南市西南部淮南煤田南部煤矿区沉陷水域</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>116.9042</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>32.6639</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>光伏电站对沉陷塘冬季水质和浮游植物群落结构的影响_王兴明.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>民勤新能源风电场典型植物土壤碳密度估算及其空间分布特征</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>宋</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>干旱地区农业研究</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2023年8月</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>甘肃省武威市民勤县红砂岗镇新能源（风电）项目工程区</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>102.4647</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>38.8992</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>民勤新能源风电场典型植物土壤碳密度估算及其空间分布特征_宋达成.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>沙区光伏电站不同植物恢复措施土壤水分特征</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>孟</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>水土保持通报</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2023年7月</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>内蒙古自治区鄂尔多斯市杭锦旗独贵塔拉镇亿利200 WP光伏园区</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>109.4583</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>38.5833</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>沙区光伏电站不同植物恢复措施土壤水分特征_孟芮冰.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>不同光伏阵列建设对荒漠草地植物群落自然恢复和土壤理化性质的影响</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>吴</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>草业科学</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2023年8月</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>陕西省榆林市靖边县伊当湾100 MW光伏电站</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>108.6356</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>37.6486</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>不同光伏阵列建设对荒漠草地植物群落自然恢复和土壤理化性质的影响_吴彤.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>滇中石漠化地区光伏阵列对微气候-土壤的影响机制及效应</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Che</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>水土保持学报</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2023年3月至9月</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>云南省石林县石林光伏电站二期工程</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>103.407222</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>24.842222</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>滇中石漠化地区光伏阵列对微气候-土壤的影响机制及效应_车光欣.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Regulatory effect of agriphotovoltaic systems with different panel heights on the thermal environment</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Gong</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Scientific Reports</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2023年7月</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>江苏省南京市光伏农业园区</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>119.18</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>31.62</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Regulatory effect of agriphotovoltaic systems with different panel heights on the thermal environment.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>光伏电站建设对植物群落与土壤特征的影响</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>鲍</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>草业学报</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2022年8月</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>宁夏回族自治区银川市宁东镇和吴忠市高沙窝镇</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>106.73</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>38.01</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>光伏电站建设对植物群落与土壤特征的影响_鲍平安.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Short-term ecological effects of solar energy development depend on plant community, soil type and disturbance intensity</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>英文</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Karban</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>J Appl Ecol</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2021年至2023年</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>莫哈韦沙漠，双子座太阳能项目，拉斯维加斯东北约50公里处</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-114.75</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>36.46666666666667</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Short-term ecological effects of solar energy development depend on plant community, soil type and disturbance intensity.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Soil microbial networks’ complexity as a primary driver of multifunctionality in photovoltaic power plants in the northwest region of China</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>英文</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Zhao</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Frontiers in Microbiology</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>未明确说明具体研究时间，但文中提及收集了2013-2023年的气象数据，并分析了不同建成年份（如2011, 2012, 2013, 2016, 2017, 2018, 2020）的光伏电站。</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>中国宁夏回族自治区（具体区域包括大武口、平罗、简泉、银川、宁东、红寺堡、石沟驿等地）</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>105.8972</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>38.7678</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Soil microbial networks' complexity as a primary driver of multifunctionality in photovoltaic power plants in the northwest region of China.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>光伏阵列对松嫩草地土壤细菌群落组成与多样性的影响</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Wang</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>东北师大学报（自然科学版）</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2021年8月</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>吉林省长岭县宏华光伏电站</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>123.95</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>光伏阵列对松嫩草地土壤细菌群落组成与多样性的影响_王诗雯.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>光伏⁃蚯蚓模式与有机物料施用对土壤质量的影响</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>肖</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>应用生态学报</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2022年10月至2023年10月</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>广东省清远市阳山县太平镇</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>112.55</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>24.2333</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>光伏-蚯蚓模式与有机物料施用对土壤质量的影响_肖远业.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>不同菌肥对风电基地退化草地土壤改良作用的研究</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>史</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>山西林业科技</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2022年6月至2022年9月</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>山西省沁源县王陶镇花坡村东部的风电基地草地</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>不同菌肥对风电基地退化草地土壤改良作用的研究_史雅楠.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>农光互补模式对海州露天矿排土场土壤的影响</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>张</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>山西农业科学</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2023年秋季与2024年春季</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>辽宁省阜新市海州露天矿排土场北侧的光伏电站内</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>121.6667</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>41.9333</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>农光互补模式对海州露天矿排土场土壤的影响_张靖涵.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Positive soil responses to different vegetation restoration measures in desert photovoltaic power stations</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>英文</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Meng</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Frontiers in Plant Science</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2022年7月</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>内蒙古自治区鄂尔多斯市杭锦旗独贵塔拉工业园区，库布齐沙漠北缘</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>109.4583</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>38.5833</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Positive soil responses to different vegetation restoration measures in desert photovoltaic power stations.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Effects of photovoltaic panels on soil temperature and moisture in desert areas</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Yue</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Environmental Science and Pollution Research</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2019年1月至12月</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>青海省共和县以南约18公里处的共和光伏电站</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>100.574</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>36.130</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Effects of photovoltaic panels on soil temperature and moisture in desert areas.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>光伏区异质环境下土壤理化特性及化学计量特征分析</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>杜</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>草地学报</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2023年10月</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>新疆维吾尔自治区伊犁哈萨克自治州尼勒克县光伏基地</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>82.071111</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>43.927778</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>光伏区异质环境下土壤理化特性及化学计量特征分析_杜孝东.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Ecohydrological effects of photovoltaic solar farms on soil microclimates and moisture regimes in arid Northwest China: A modeling study</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>英文</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Wu</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Science of the Total Environment</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>未明确说明，但数据收集期为1980-2017年，模型模拟期为100年</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>甘肃省武威市丰乐镇（位于河西走廊东部的戈壁沙漠地区）</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>102.329722</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>38.102222</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Ecohydrological effects of photovoltaic solar farms on soil microclimates and moisture regimes in arid Northwest China-A modeling study.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Agrivoltaics system: sustainable approach for okra cultivation and energy stability</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>英文</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Islam</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Plant Science Today</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2023年11月至2024年7月</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>西孟加拉邦南24帕尔加纳斯区The Neotia大学校园</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>88.0625</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>21.48333333</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Agrivoltaics system-Sustainable approach for okra cultivation and.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>不同植被恢复类型下土壤碳含量对光伏组件遮阴的响应</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>罗</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>西北农林科技大学学报(自然科学版)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2021年10月</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>云南省昆明市东川光伏电站</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>103.141944</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>26.165556</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>不同植被恢复类型下土壤碳含量对光伏组件遮阴的响应_罗忠新.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>How a photovoltaic panel impacts rainfall-runoff and soil erosion processes on slopes at the plot scale</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Wang</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Journal of Hydrology</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2021年10月24日至2021年11月25日</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>陕西省韩城市附近</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>110.39</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>35.31</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>How a photovoltaic panel impacts rainfall-runoff and soil erosion processes on slopes at the plot scale.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Can Grasslands in Photovoltaic Parks Play a Role in Conserving Soil Arthropod Biodiversity?</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>英文</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Menta</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2021年6月和2021年10月</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>意大利</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>伦巴第大区古夏纳和艾米利亚-罗马涅大区锡萨</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Can Grasslands in Photovoltaic Parks Play a Role in Conserving Soil Arthropod Biodiversity.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>山地风电场建设对土壤性质和植被覆盖的影响———以云南省将军山风电场为例</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>生态学杂志</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2021年10月</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>云南省玉溪市华宁县将军山风电场</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>103.0125</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>24.24875</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>山地风电场建设对土壤性质和植被覆盖的影响——以云南省将军山风电场为例_张力琛.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Environmental Heterogeneity Imposed by Photovoltaic Array Alters Grassland Soil Microbial Communities</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>英文</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Siggers</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Global Change Biology</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2023年5月至9月</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>科罗拉多州朗蒙特市杰克太阳能花园</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>-105.12936</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>40.12191</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Environmental Heterogeneity Imposed by Photovoltaic Array Alters Grassland Soil Microbial Communities.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>风电项目对潜在生态廊道的影响———基于MSPA－MCＲ模型</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>艾</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>生态学报</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>未明确说明（研究使用了2000年和2020年的遥感影像数据）</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>福建省平潭岛北部陆上风电项目所在区域，包括白青乡、平原镇及长江澳部分区域</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>119.78</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>25.51</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>风电项目对潜在生态廊道的影响——基于MSPA-MCR模型_艾婧文.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>风电机建设对内蒙古温性草原植物多样性和土壤生态化学计量的影响</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>郭</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>草原与草坪</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2023年8月</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>内蒙古自治区呼伦贝尔盟西部新巴尔虎右旗</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>116.623</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>48.717</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>风电机建设对内蒙古温性草原植物多样性和土壤生态化学计量的影响_郭彦君.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Prioritizing landscapes for mitigating the impacts of onshore wind farms on multidimensional waterbird diversity in the Yellow Sea</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>英文</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Zhao</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Current Zoology</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2019年12月至2021年3月</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>黄海海岸（从江苏省灌河口至上海市长江口）</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>119.894622</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>31.508781</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Prioritizing landscapes for mitigating the impacts of onshore wind farms on multidimensional waterbird diversity in the Yellow Sea.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Using intelligent water purification and ecological conservation system to improve environmental conservation benefits evaluation</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>英文</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Huang</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Environmental Technology &amp; Innovation</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2021年11月24日至2022年10月16日</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>台湾南投县鹿谷乡麒麟湖</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>120.7730556</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>23.7525</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Using intelligent water purification and ecological conservation system to improve environmental conservation benefits evaluation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Can wind farms change the phenology of grassland in China?</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Liu</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Science of the Total Environment</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2000年至2020年</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>内蒙古自治区锡林郭勒盟半干旱草原区</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>116.05</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>43.44</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Can wind farms change the phenology of grassland in China.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>不同光伏阵列处理对滇中石漠化地区环境因子及细菌群落组成和多样性的影响</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>吴</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>生态环境学报</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2023年4月</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>云南省昆明市石林彝族自治县云南石林光伏电站试验示范区</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>103.428611</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>24.842222</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>不同光伏阵列处理对滇中石漠化地区环境因子及细菌群落组成和多样性的影响_吴雲鹏.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>光伏电站土壤微量元素有效含量化学计量对植被恢复的响应</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>武</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>水土保持通报</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2023年6月</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>内蒙古自治区呼和浩特市土默特左旗大有光能源30 MWp光伏电站（光伏农林牧示范基地）</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>110.7833</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>40.6</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>光伏电站土壤微量元素有效含量化学计量对植被恢复的响应_武燕.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>光伏系统对典型草原露天煤矿排土场生态修复效果的影响</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>王</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>内蒙古大学学报(自然科学版)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2024年8月</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>内蒙古自治区锡林郭勒盟锡林浩特市宝力根苏木胜利能源分公司露天煤矿排土场</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>116.0167</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>43.9667</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>光伏系统对典型草原露天煤矿排土场生态修复效果的影响_王逸飞.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>内蒙古中部草原区光伏电站对土壤水分及其脉冲响应的作用机制</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>翟</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>太阳能学报</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2018年6月至8月</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>内蒙古土默川平原境内209国道东侧的山路能源集团大有光能源30 MWP光伏农林牧示范基地</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>110.8</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>40.4333</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>内蒙古中部草原区光伏电站对土壤水分及其脉冲响应的作用机制_翟波.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>青藏高原荒漠区典型光伏电站建设对植被属性和土壤性质的影响</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Hao</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>生态学报</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2023年8月、2024年8月</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>青海省海南州共和县塔拉滩光伏产业园</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>100.25</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>36.35</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>青藏高原荒漠区典型光伏电站建设对植被属性和土壤性质的影响_郝晓珍.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>不同作物种植对光伏坡地土壤团聚体稳定性与有机碳的影响</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>李</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>农业环境科学学报</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2022年7月</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>广东省清远市阳山县太平镇光伏农业坡地项目区</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>112.55</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>24.2333</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>不同作物种植对光伏坡地土壤团聚体稳定性与有机碳的影响_李馨妤.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Large-scale photovoltaic farms significantly change the vegetation diversity and biomass through influencing soil moisture and physiochemical properties</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Yue</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vadose Zone Journal</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2020年7月和9月</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>青海省共和县共和光伏电站</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>100.5083</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>36.0333</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Large-scale photovoltaic farms significantly change the vegetation diversity and biomass through influencing soil moisture and physiochemical properties.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Positive ecological effects of wind farms on vegetation in China’s Gobi desert</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Xu</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Scientific Reports</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2016年6月至8月</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>甘肃省酒泉市瓜州县第一瓜州风电场</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>95.2875</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>40.675</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Positive ecological effects of wind farms on vegetation in China's Gobi desert.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>青藏高原东北缘大规模光伏电站对高寒沙地植被－土壤的影响研究—以青海共和盆地为例</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>屈</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>干旱区资源与环境</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2023年7月</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>青海省海南藏族自治州共和县塔拉滩光伏产业园区（一塔拉区中北部，西丽高速公路以东，龙羊峡水库以西，北距共和县城约18km）</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>100.6</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>36.27</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>青藏高原东北缘大规模光伏电站对高寒沙地植被-土壤的影响研究——以青海共和盆地为例_屈准.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Landscape features associated to wind farms increase mammalian predator abundance and ground‑nest predation</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Gómez‑Catasús</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Biodiversity and Conservation</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2016年4月、5月、6月</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>西班牙</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>索里亚省南部“Tierra de Medinaceli”地区</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>-2.443083</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>41.191361</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Landscape features associated to wind farms increase mammalian predator abundance and ground-nest predation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>沙区追踪式光伏阵列区域土壤养分空间分异特征</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>袁</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>中国农业科技导报</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2023年7月</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>内蒙古鄂尔多斯市达拉特旗昭君镇中广核格桑领跑者光伏基地</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>109.6833</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>40.3000</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>沙区追踪式光伏阵列区域土壤养分空间分异特征_袁嘉茂.pdf</t>
         </is>
       </c>
     </row>
